--- a/01_Input/00_CO Validation/Bolivia - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Bolivia - Energy Projects.xlsx
@@ -423,6 +423,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K4" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L4" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1004,15 +1024,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K4" s="22" t="n">
+      <c r="K4" s="40" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="40" t="n"/>
-      <c r="M4" s="40" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M4" s="22" t="n"/>
       <c r="N4" s="23" t="n"/>
       <c r="O4" s="41" t="n"/>
       <c r="P4" s="42" t="n"/>
@@ -1116,7 +1132,7 @@
       <c r="X6" s="2" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="Q2:Q3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -1147,14 +1163,9 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
